--- a/XBRL-template-MFRS/Company/03-SOPL-Function.xlsx
+++ b/XBRL-template-MFRS/Company/03-SOPL-Function.xlsx
@@ -628,6 +628,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="12">
       <c r="A3" s="28" t="inlineStr">
         <is>
@@ -1029,11 +1030,11 @@
         </is>
       </c>
       <c r="B36" s="36">
-        <f>1*B35</f>
+        <f>1*B34+1*B35</f>
         <v/>
       </c>
       <c r="C36" s="36">
-        <f>1*C35</f>
+        <f>1*C34+1*C35</f>
         <v/>
       </c>
       <c r="D36" s="40" t="n"/>
@@ -1075,11 +1076,11 @@
         </is>
       </c>
       <c r="B40" s="36">
-        <f>1*B39</f>
+        <f>1*B38+1*B39</f>
         <v/>
       </c>
       <c r="C40" s="36">
-        <f>1*C39</f>
+        <f>1*C38+1*C39</f>
         <v/>
       </c>
       <c r="D40" s="40" t="n"/>
@@ -1123,6 +1124,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="12">
       <c r="A3" s="28" t="inlineStr">
         <is>
@@ -1936,11 +1938,11 @@
         </is>
       </c>
       <c r="B79" s="36">
-        <f>1*B75+1*B76+1*B77+1*B78</f>
+        <f>1*B74+1*B75+1*B76+1*B77+1*B78</f>
         <v/>
       </c>
       <c r="C79" s="36">
-        <f>1*C75+1*C76+1*C77+1*C78</f>
+        <f>1*C74+1*C75+1*C76+1*C77+1*C78</f>
         <v/>
       </c>
       <c r="D79" s="40" t="n"/>
@@ -2052,11 +2054,11 @@
         </is>
       </c>
       <c r="B90" s="36">
-        <f>1*B49+1*B50+1*B51+1*B52+1*B53+1*B54+1*B55+1*B56+1*B57+1*B58+1*B59+1*B63+1*B68+1*B69+1*B70+1*B71+1*B72+1*B99+1*B80+1*B81+1*B82+1*B85+1*B86+1*B87+1*B88+1*B89+1*B84+1*B83</f>
+        <f>1*B49+1*B50+1*B51+1*B52+1*B53+1*B54+1*B55+1*B56+1*B57+1*B58+1*B59+1*B63+1*B68+1*B69+1*B70+1*B71+1*B72+1*B79+1*B80+1*B81+1*B82+1*B83+1*B84+1*B85+1*B86+1*B87+1*B88+1*B89</f>
         <v/>
       </c>
       <c r="C90" s="36">
-        <f>1*C49+1*C50+1*C51+1*C52+1*C53+1*C54+1*C55+1*C56+1*C57+1*C58+1*C59+1*C63+1*C68+1*C69+1*C70+1*C71+1*C72+1*C99+1*C80+1*C81+1*C82+1*C85+1*C86+1*C87+1*C88+1*C89+1*C84+1*C83</f>
+        <f>1*C49+1*C50+1*C51+1*C52+1*C53+1*C54+1*C55+1*C56+1*C57+1*C58+1*C59+1*C63+1*C68+1*C69+1*C70+1*C71+1*C72+1*C79+1*C80+1*C81+1*C82+1*C83+1*C84+1*C85+1*C86+1*C87+1*C88+1*C89</f>
         <v/>
       </c>
       <c r="D90" s="40" t="n"/>
